--- a/data/dividends_info_20260502.xlsx
+++ b/data/dividends_info_20260502.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K180"/>
+  <dimension ref="A1:K170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3969,11 +3969,11 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.75</v>
+        <v>0.27</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -3992,19 +3992,19 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>IT0003121677</t>
+          <t>IT0003132476</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>15.0600004196167</v>
+        <v>24</v>
       </c>
       <c r="I76" t="n">
-        <v>4.980079542514971</v>
+        <v>1.125</v>
       </c>
       <c r="J76" t="n">
         <v>16</v>
@@ -4016,11 +4016,11 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -4044,14 +4044,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>NL0013995087</t>
+          <t>IT0005521247</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15.14999961853027</v>
+        <v>8.439999580383301</v>
       </c>
       <c r="I77" t="n">
-        <v>1.980198069662417</v>
+        <v>2.369668364259765</v>
       </c>
       <c r="J77" t="n">
         <v>16</v>
@@ -4063,11 +4063,11 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.85</v>
+        <v>0.24</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -4091,14 +4091,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>IT0005246191</t>
+          <t>IT0004967292</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>46.20000076293945</v>
+        <v>9.300000190734863</v>
       </c>
       <c r="I78" t="n">
-        <v>1.839826809444232</v>
+        <v>2.580645108363549</v>
       </c>
       <c r="J78" t="n">
         <v>16</v>
@@ -4110,11 +4110,11 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -4138,14 +4138,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>IT0003115950</t>
+          <t>IT0000072170</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>33.04000091552734</v>
+        <v>21.07999992370605</v>
       </c>
       <c r="I79" t="n">
-        <v>2.572639153894628</v>
+        <v>3.747628097055092</v>
       </c>
       <c r="J79" t="n">
         <v>16</v>
@@ -4157,11 +4157,11 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1.3</v>
+        <v>0.093</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -4185,14 +4185,14 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>IT0003492391</t>
+          <t>IT0005345233</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>58.02000045776367</v>
+        <v>5.119999885559082</v>
       </c>
       <c r="I80" t="n">
-        <v>2.240606669671349</v>
+        <v>1.816406290599844</v>
       </c>
       <c r="J80" t="n">
         <v>16</v>
@@ -4204,11 +4204,11 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6</v>
+        <v>0.06</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -4227,19 +4227,19 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>IT0001463063</t>
+          <t>IT0005359101</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>8.100000381469727</v>
+        <v>6.25</v>
       </c>
       <c r="I81" t="n">
-        <v>7.407407058555364</v>
+        <v>0.96</v>
       </c>
       <c r="J81" t="n">
         <v>16</v>
@@ -4251,11 +4251,11 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.47</v>
+        <v>0.35</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -4279,14 +4279,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>IT0005669558</t>
+          <t>IT0001078911</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>5.900000095367432</v>
+        <v>35.77999877929688</v>
       </c>
       <c r="I82" t="n">
-        <v>7.966101566151415</v>
+        <v>0.978200145167467</v>
       </c>
       <c r="J82" t="n">
         <v>16</v>
@@ -4298,11 +4298,11 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.2</v>
+        <v>0.5543</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -4321,19 +4321,19 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>IT0005312027</t>
+          <t>IT0005090300</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>5.920000076293945</v>
+        <v>7.224999904632568</v>
       </c>
       <c r="I83" t="n">
-        <v>3.378378334839559</v>
+        <v>7.67197241960641</v>
       </c>
       <c r="J83" t="n">
         <v>16</v>
@@ -4345,11 +4345,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4373,14 +4373,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>IT0001157020</t>
+          <t>IT0001077780</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>22.97999954223633</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I84" t="n">
-        <v>4.351610182419889</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J84" t="n">
         <v>16</v>
@@ -4392,11 +4392,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.215</v>
+        <v>0.2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -4420,14 +4420,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>IT0004356751</t>
+          <t>IT0003411417</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>4.71999979019165</v>
+        <v>12.60000038146973</v>
       </c>
       <c r="I85" t="n">
-        <v>4.555084948240435</v>
+        <v>1.587301539245438</v>
       </c>
       <c r="J85" t="n">
         <v>16</v>
@@ -4439,11 +4439,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.27</v>
+        <v>0.103</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -4457,40 +4457,40 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-05-20</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>IT0003132476</t>
+          <t>IT0005186371</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>24</v>
+        <v>6.190000057220459</v>
       </c>
       <c r="I86" t="n">
-        <v>1.125</v>
+        <v>1.663974136476031</v>
       </c>
       <c r="J86" t="n">
         <v>16</v>
       </c>
       <c r="K86" t="n">
-        <v>18</v>
+        <v>-347</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -4514,14 +4514,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>IT0005521247</t>
+          <t>IT0000072618</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>8.439999580383301</v>
+        <v>5.775000095367432</v>
       </c>
       <c r="I87" t="n">
-        <v>2.369668364259765</v>
+        <v>3.290043235712039</v>
       </c>
       <c r="J87" t="n">
         <v>16</v>
@@ -4533,11 +4533,11 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.24</v>
+        <v>0.432</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -4561,14 +4561,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>IT0004967292</t>
+          <t>IT0005211237</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>9.300000190734863</v>
+        <v>10.28999996185303</v>
       </c>
       <c r="I88" t="n">
-        <v>2.580645108363549</v>
+        <v>4.198250744426682</v>
       </c>
       <c r="J88" t="n">
         <v>16</v>
@@ -4580,11 +4580,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.79</v>
+        <v>0.44</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4608,14 +4608,14 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>IT0000072170</t>
+          <t>IT0005541336</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>21.07999992370605</v>
+        <v>25.07999992370605</v>
       </c>
       <c r="I89" t="n">
-        <v>3.747628097055092</v>
+        <v>1.754385970249164</v>
       </c>
       <c r="J89" t="n">
         <v>16</v>
@@ -4627,11 +4627,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.093</v>
+        <v>0.03</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -4655,14 +4655,14 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>IT0005345233</t>
+          <t>IT0004522162</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.119999885559082</v>
+        <v>1.059999942779541</v>
       </c>
       <c r="I90" t="n">
-        <v>1.816406290599844</v>
+        <v>2.830188832023306</v>
       </c>
       <c r="J90" t="n">
         <v>16</v>
@@ -4674,11 +4674,11 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.06</v>
+        <v>0.47</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4697,19 +4697,19 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>IT0005359101</t>
+          <t>IT0003428445</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>6.25</v>
+        <v>8.590000152587891</v>
       </c>
       <c r="I91" t="n">
-        <v>0.96</v>
+        <v>5.471478366137212</v>
       </c>
       <c r="J91" t="n">
         <v>16</v>
@@ -4721,11 +4721,11 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Moncler S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.35</v>
+        <v>1.4</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -4749,14 +4749,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>IT0001078911</t>
+          <t>IT0004965148</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>35.77999877929688</v>
+        <v>51.2400016784668</v>
       </c>
       <c r="I92" t="n">
-        <v>0.978200145167467</v>
+        <v>2.732240347658573</v>
       </c>
       <c r="J92" t="n">
         <v>16</v>
@@ -4768,11 +4768,11 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5543</v>
+        <v>0.3</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4796,14 +4796,14 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>IT0005090300</t>
+          <t>IT0005366767</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>7.224999904632568</v>
+        <v>4.047999858856201</v>
       </c>
       <c r="I93" t="n">
-        <v>7.67197241960641</v>
+        <v>7.411067452081574</v>
       </c>
       <c r="J93" t="n">
         <v>16</v>
@@ -4815,11 +4815,11 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4843,14 +4843,14 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>IT0001077780</t>
+          <t>IT0005594418</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>2.259999990463257</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="I94" t="n">
-        <v>2.654867267840171</v>
+        <v>0.9836065727547595</v>
       </c>
       <c r="J94" t="n">
         <v>16</v>
@@ -4862,11 +4862,11 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4890,14 +4890,14 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>IT0003411417</t>
+          <t>IT0005453748</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>12.60000038146973</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="I95" t="n">
-        <v>1.587301539245438</v>
+        <v>4.82954548071485</v>
       </c>
       <c r="J95" t="n">
         <v>16</v>
@@ -4909,11 +4909,11 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.103</v>
+        <v>0.7</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2025-05-20</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4937,30 +4937,30 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>IT0005186371</t>
+          <t>IT0005373789</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>6.190000057220459</v>
+        <v>21.79999923706055</v>
       </c>
       <c r="I96" t="n">
-        <v>1.663974136476031</v>
+        <v>3.211009286688334</v>
       </c>
       <c r="J96" t="n">
         <v>16</v>
       </c>
       <c r="K96" t="n">
-        <v>-347</v>
+        <v>18</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.19</v>
+        <v>0.035</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4984,14 +4984,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>IT0000072618</t>
+          <t>IT0005378143</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.775000095367432</v>
+        <v>2.539999961853027</v>
       </c>
       <c r="I97" t="n">
-        <v>3.290043235712039</v>
+        <v>1.377952776600286</v>
       </c>
       <c r="J97" t="n">
         <v>16</v>
@@ -5003,11 +5003,11 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.432</v>
+        <v>0.33</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -5031,14 +5031,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>IT0005211237</t>
+          <t>IT0005054967</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10.28999996185303</v>
+        <v>6.119999885559082</v>
       </c>
       <c r="I98" t="n">
-        <v>4.198250744426682</v>
+        <v>5.392156963575718</v>
       </c>
       <c r="J98" t="n">
         <v>16</v>
@@ -5050,11 +5050,11 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.44</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -5078,14 +5078,14 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>IT0005541336</t>
+          <t>IT0004931496</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>25.07999992370605</v>
+        <v>0.9660000205039978</v>
       </c>
       <c r="I99" t="n">
-        <v>1.754385970249164</v>
+        <v>7.246376657784999</v>
       </c>
       <c r="J99" t="n">
         <v>16</v>
@@ -5097,11 +5097,11 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.03</v>
+        <v>0.71</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -5125,14 +5125,14 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>IT0004522162</t>
+          <t>IT0003828271</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1.059999942779541</v>
+        <v>49.63999938964844</v>
       </c>
       <c r="I100" t="n">
-        <v>2.830188832023306</v>
+        <v>1.430298164242238</v>
       </c>
       <c r="J100" t="n">
         <v>16</v>
@@ -5144,11 +5144,11 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.47</v>
+        <v>1.35</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -5172,14 +5172,14 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>IT0003428445</t>
+          <t>IT0005282865</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>8.590000152587891</v>
+        <v>94.30000305175781</v>
       </c>
       <c r="I101" t="n">
-        <v>5.471478366137212</v>
+        <v>1.431601226204664</v>
       </c>
       <c r="J101" t="n">
         <v>16</v>
@@ -5191,11 +5191,11 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Moncler S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>1.4</v>
+        <v>0.08</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -5219,14 +5219,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>IT0004965148</t>
+          <t>IT0005543613</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>51.2400016784668</v>
+        <v>7</v>
       </c>
       <c r="I102" t="n">
-        <v>2.732240347658573</v>
+        <v>1.142857142857143</v>
       </c>
       <c r="J102" t="n">
         <v>16</v>
@@ -5238,11 +5238,11 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.3</v>
+        <v>3</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -5266,14 +5266,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>IT0005366767</t>
+          <t>IT0001017851</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>4.047999858856201</v>
+        <v>256</v>
       </c>
       <c r="I103" t="n">
-        <v>7.411067452081574</v>
+        <v>1.171875</v>
       </c>
       <c r="J103" t="n">
         <v>16</v>
@@ -5285,11 +5285,11 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -5313,14 +5313,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>IT0005594418</t>
+          <t>IT0005495657</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>12.19999980926514</v>
+        <v>4.605999946594238</v>
       </c>
       <c r="I104" t="n">
-        <v>0.9836065727547595</v>
+        <v>3.690838080137217</v>
       </c>
       <c r="J104" t="n">
         <v>16</v>
@@ -5332,11 +5332,11 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.17</v>
+        <v>0.297</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -5360,14 +5360,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>IT0005453748</t>
+          <t>IT0005568461</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>3.519999980926514</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I105" t="n">
-        <v>4.82954548071485</v>
+        <v>3.933774735058545</v>
       </c>
       <c r="J105" t="n">
         <v>16</v>
@@ -5379,11 +5379,11 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7</v>
+        <v>0.45</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -5407,14 +5407,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>IT0005373789</t>
+          <t>IT0001206769</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>21.79999923706055</v>
+        <v>57.59999847412109</v>
       </c>
       <c r="I106" t="n">
-        <v>3.211009286688334</v>
+        <v>0.7812500206960578</v>
       </c>
       <c r="J106" t="n">
         <v>16</v>
@@ -5426,11 +5426,11 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -5454,14 +5454,14 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>IT0005378143</t>
+          <t>IT0005595423</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2.539999961853027</v>
+        <v>4.869999885559082</v>
       </c>
       <c r="I107" t="n">
-        <v>1.377952776600286</v>
+        <v>0.8213552554407904</v>
       </c>
       <c r="J107" t="n">
         <v>16</v>
@@ -5473,11 +5473,11 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.33</v>
+        <v>1.05</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>IT0005054967</t>
+          <t>IT0003549422</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.119999885559082</v>
+        <v>33.08000183105469</v>
       </c>
       <c r="I108" t="n">
-        <v>5.392156963575718</v>
+        <v>3.174123161668891</v>
       </c>
       <c r="J108" t="n">
         <v>16</v>
@@ -5520,11 +5520,11 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5548,14 +5548,14 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>IT0004931496</t>
+          <t>IT0005621070</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9660000205039978</v>
+        <v>1.549999952316284</v>
       </c>
       <c r="I109" t="n">
-        <v>7.246376657784999</v>
+        <v>3.225806550850609</v>
       </c>
       <c r="J109" t="n">
         <v>16</v>
@@ -5567,11 +5567,11 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.71</v>
+        <v>0.38</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -5595,14 +5595,14 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>IT0003828271</t>
+          <t>IT0005162406</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>49.63999938964844</v>
+        <v>20.04000091552734</v>
       </c>
       <c r="I110" t="n">
-        <v>1.430298164242238</v>
+        <v>1.896207498202105</v>
       </c>
       <c r="J110" t="n">
         <v>16</v>
@@ -5614,15 +5614,15 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>1.35</v>
+        <v>0.6</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5642,14 +5642,14 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>IT0005282865</t>
+          <t>LU2598331598</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>94.30000305175781</v>
+        <v>27.22999954223633</v>
       </c>
       <c r="I111" t="n">
-        <v>1.431601226204664</v>
+        <v>2.203452111959615</v>
       </c>
       <c r="J111" t="n">
         <v>16</v>
@@ -5661,11 +5661,11 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.08</v>
+        <v>0.35</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5689,14 +5689,14 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>IT0005543613</t>
+          <t>IT0001454435</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>7</v>
+        <v>32.70000076293945</v>
       </c>
       <c r="I112" t="n">
-        <v>1.142857142857143</v>
+        <v>1.070336366464775</v>
       </c>
       <c r="J112" t="n">
         <v>16</v>
@@ -5708,11 +5708,11 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3</v>
+        <v>0.017</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -5736,14 +5736,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>IT0001017851</t>
+          <t>IT0005658841</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>256</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="I113" t="n">
-        <v>1.171875</v>
+        <v>0.4722222347318393</v>
       </c>
       <c r="J113" t="n">
         <v>16</v>
@@ -5755,11 +5755,11 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.17</v>
+        <v>0.01</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5783,14 +5783,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>IT0005495657</t>
+          <t>IT0005573065</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>4.605999946594238</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="I114" t="n">
-        <v>3.690838080137217</v>
+        <v>0.3558718933676701</v>
       </c>
       <c r="J114" t="n">
         <v>16</v>
@@ -5802,11 +5802,11 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.297</v>
+        <v>1.12</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -5830,14 +5830,14 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>IT0005568461</t>
+          <t>IT0004810054</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>7.550000190734863</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="I115" t="n">
-        <v>3.933774735058545</v>
+        <v>5.045044871663794</v>
       </c>
       <c r="J115" t="n">
         <v>16</v>
@@ -5849,11 +5849,11 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5877,14 +5877,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>IT0001206769</t>
+          <t>IT0004717200</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>57.59999847412109</v>
+        <v>1.539999961853027</v>
       </c>
       <c r="I116" t="n">
-        <v>0.7812500206960578</v>
+        <v>6.493506654355598</v>
       </c>
       <c r="J116" t="n">
         <v>16</v>
@@ -5896,11 +5896,11 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.04</v>
+        <v>0.26</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5924,14 +5924,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>IT0005595423</t>
+          <t>IT0003865588</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.869999885559082</v>
+        <v>8.800000190734863</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8213552554407904</v>
+        <v>2.954545390507408</v>
       </c>
       <c r="J117" t="n">
         <v>16</v>
@@ -5943,11 +5943,11 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>1.05</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -5971,14 +5971,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>IT0003549422</t>
+          <t>IT0005610958</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>33.08000183105469</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I118" t="n">
-        <v>3.174123161668891</v>
+        <v>4.395238294839327</v>
       </c>
       <c r="J118" t="n">
         <v>16</v>
@@ -5990,11 +5990,11 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6018,30 +6018,30 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>IT0005621070</t>
+          <t>IT0001006128</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>1.549999952316284</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I119" t="n">
-        <v>3.225806550850609</v>
+        <v>3.804347904958889</v>
       </c>
       <c r="J119" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K119" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.38</v>
+        <v>0.096</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -6050,12 +6050,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6065,44 +6065,44 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>IT0005162406</t>
+          <t>IT0005543332</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>20.04000091552734</v>
+        <v>5.150000095367432</v>
       </c>
       <c r="I120" t="n">
-        <v>1.896207498202105</v>
+        <v>1.86407763538402</v>
       </c>
       <c r="J120" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K120" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6112,30 +6112,30 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>LU2598331598</t>
+          <t>IT0005416281</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>27.22999954223633</v>
+        <v>6.199999809265137</v>
       </c>
       <c r="I121" t="n">
-        <v>2.203452111959615</v>
+        <v>4.838709826275912</v>
       </c>
       <c r="J121" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K121" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -6144,12 +6144,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6159,30 +6159,30 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>IT0001454435</t>
+          <t>IT0005037905</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>32.70000076293945</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I122" t="n">
-        <v>1.070336366464775</v>
+        <v>1.70940173726859</v>
       </c>
       <c r="J122" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K122" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.017</v>
+        <v>0.06</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -6191,45 +6191,45 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Interim</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>IT0005658841</t>
+          <t>IT0005337818</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>3.599999904632568</v>
+        <v>9.600000381469727</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4722222347318393</v>
+        <v>0.6249999751647324</v>
       </c>
       <c r="J123" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K123" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -6238,12 +6238,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6253,30 +6253,30 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>IT0005573065</t>
+          <t>IT0005075764</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>2.809999942779541</v>
+        <v>19.81999969482422</v>
       </c>
       <c r="I124" t="n">
-        <v>0.3558718933676701</v>
+        <v>2.522704377894464</v>
       </c>
       <c r="J124" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K124" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>1.12</v>
+        <v>0.06</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -6285,12 +6285,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6300,30 +6300,30 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>IT0004810054</t>
+          <t>IT0004376858</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>22.20000076293945</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="I125" t="n">
-        <v>5.045044871663794</v>
+        <v>2.608695706257524</v>
       </c>
       <c r="J125" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K125" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -6332,12 +6332,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6347,30 +6347,30 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>IT0004717200</t>
+          <t>IT0005138703</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1.539999961853027</v>
+        <v>16.28000068664551</v>
       </c>
       <c r="I126" t="n">
-        <v>6.493506654355598</v>
+        <v>3.071252941716091</v>
       </c>
       <c r="J126" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K126" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.26</v>
+        <v>0.1</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -6379,12 +6379,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6394,30 +6394,30 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>IT0003865588</t>
+          <t>IT0005430951</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>8.800000190734863</v>
+        <v>4.019999980926514</v>
       </c>
       <c r="I127" t="n">
-        <v>2.954545390507408</v>
+        <v>2.487562200857334</v>
       </c>
       <c r="J127" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K127" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6441,30 +6441,30 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>IT0005610958</t>
+          <t>IT0005339160</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.099999904632568</v>
+        <v>3.480000019073486</v>
       </c>
       <c r="I128" t="n">
-        <v>4.395238294839327</v>
+        <v>3.160919522905243</v>
       </c>
       <c r="J128" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K128" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.35</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -6488,14 +6488,14 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>IT0001006128</t>
+          <t>IT0005545238</t>
         </is>
       </c>
       <c r="H129" t="n">
         <v>9.199999809265137</v>
       </c>
       <c r="I129" t="n">
-        <v>3.804347904958889</v>
+        <v>0.923913062632873</v>
       </c>
       <c r="J129" t="n">
         <v>9</v>
@@ -6507,11 +6507,11 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.096</v>
+        <v>0.095</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -6535,14 +6535,14 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>IT0005543332</t>
+          <t>IT0005466963</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>5.150000095367432</v>
+        <v>4.889999866485596</v>
       </c>
       <c r="I130" t="n">
-        <v>1.86407763538402</v>
+        <v>1.942740339342294</v>
       </c>
       <c r="J130" t="n">
         <v>9</v>
@@ -6554,11 +6554,11 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.3</v>
+        <v>0.03</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -6582,14 +6582,14 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>IT0005416281</t>
+          <t>IT0005521551</t>
         </is>
       </c>
       <c r="H131" t="n">
-        <v>6.199999809265137</v>
+        <v>1.240000009536743</v>
       </c>
       <c r="I131" t="n">
-        <v>4.838709826275912</v>
+        <v>2.419354820102608</v>
       </c>
       <c r="J131" t="n">
         <v>9</v>
@@ -6601,11 +6601,11 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -6629,14 +6629,14 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>IT0005037905</t>
+          <t>IT0005246142</t>
         </is>
       </c>
       <c r="H132" t="n">
-        <v>11.69999980926514</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I132" t="n">
-        <v>1.70940173726859</v>
+        <v>1.184210541175673</v>
       </c>
       <c r="J132" t="n">
         <v>9</v>
@@ -6648,11 +6648,11 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -6671,19 +6671,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Interim</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>IT0005337818</t>
+          <t>IT0005532525</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.600000381469727</v>
+        <v>8.600000381469727</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6249999751647324</v>
+        <v>1.162790646096578</v>
       </c>
       <c r="J133" t="n">
         <v>9</v>
@@ -6695,11 +6695,11 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -6723,14 +6723,14 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>IT0005075764</t>
+          <t>IT0004171440</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>19.81999969482422</v>
+        <v>7.039999961853027</v>
       </c>
       <c r="I134" t="n">
-        <v>2.522704377894464</v>
+        <v>3.125000016933138</v>
       </c>
       <c r="J134" t="n">
         <v>9</v>
@@ -6742,11 +6742,11 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.06</v>
+        <v>0.61</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6770,30 +6770,30 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>IT0004376858</t>
+          <t>IT0004720733</t>
         </is>
       </c>
       <c r="H135" t="n">
-        <v>2.299999952316284</v>
+        <v>27.45000076293945</v>
       </c>
       <c r="I135" t="n">
-        <v>2.608695706257524</v>
+        <v>2.222222160458253</v>
       </c>
       <c r="J135" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K135" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -6817,30 +6817,30 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>IT0005138703</t>
+          <t>IT0005386369</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>16.28000068664551</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="I136" t="n">
-        <v>3.071252941716091</v>
+        <v>4.870129990766698</v>
       </c>
       <c r="J136" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K136" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -6849,12 +6849,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6864,30 +6864,30 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>IT0005430951</t>
+          <t>IT0001268561</t>
         </is>
       </c>
       <c r="H137" t="n">
-        <v>4.019999980926514</v>
+        <v>12.25</v>
       </c>
       <c r="I137" t="n">
-        <v>2.487562200857334</v>
+        <v>5.714285714285714</v>
       </c>
       <c r="J137" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K137" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.11</v>
+        <v>0.5105</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -6896,12 +6896,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6911,44 +6911,44 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>IT0005339160</t>
+          <t>IT0001041000</t>
         </is>
       </c>
       <c r="H138" t="n">
-        <v>3.480000019073486</v>
+        <v>9.220000267028809</v>
       </c>
       <c r="I138" t="n">
-        <v>3.160919522905243</v>
+        <v>5.536876195389864</v>
       </c>
       <c r="J138" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K138" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>EURO</t>
+          <t>DOLLARI USA</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6958,30 +6958,30 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>IT0005545238</t>
+          <t>LU2592315662</t>
         </is>
       </c>
       <c r="H139" t="n">
-        <v>9.199999809265137</v>
+        <v>8</v>
       </c>
       <c r="I139" t="n">
-        <v>0.923913062632873</v>
+        <v>3.375</v>
       </c>
       <c r="J139" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K139" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.095</v>
+        <v>0.35</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7005,30 +7005,30 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>IT0005466963</t>
+          <t>IT0003850929</t>
         </is>
       </c>
       <c r="H140" t="n">
-        <v>4.889999866485596</v>
+        <v>5.744999885559082</v>
       </c>
       <c r="I140" t="n">
-        <v>1.942740339342294</v>
+        <v>6.092254255387845</v>
       </c>
       <c r="J140" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K140" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.03</v>
+        <v>1.1</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -7037,12 +7037,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7052,30 +7052,30 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>IT0005521551</t>
+          <t>IT0005203424</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1.240000009536743</v>
+        <v>39</v>
       </c>
       <c r="I141" t="n">
-        <v>2.419354820102608</v>
+        <v>2.820512820512821</v>
       </c>
       <c r="J141" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K141" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.09</v>
+        <v>0.75</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -7084,45 +7084,45 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>IT0005246142</t>
+          <t>IT0005252736</t>
         </is>
       </c>
       <c r="H142" t="n">
-        <v>7.599999904632568</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="I142" t="n">
-        <v>1.184210541175673</v>
+        <v>3.97877976032976</v>
       </c>
       <c r="J142" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K142" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.1</v>
+        <v>0.43</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -7131,12 +7131,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7146,30 +7146,30 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>IT0005532525</t>
+          <t>IT0003203947</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>8.600000381469727</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I143" t="n">
-        <v>1.162790646096578</v>
+        <v>3.675213735127469</v>
       </c>
       <c r="J143" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K143" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -7178,12 +7178,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7193,30 +7193,30 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>IT0004171440</t>
+          <t>IT0005322612</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>7.039999961853027</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="I144" t="n">
-        <v>3.125000016933138</v>
+        <v>3.521126571379833</v>
       </c>
       <c r="J144" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K144" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.61</v>
+        <v>0.197169</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -7240,14 +7240,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>IT0004720733</t>
+          <t>IT0005455875</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>27.45000076293945</v>
+        <v>12.11999988555908</v>
       </c>
       <c r="I145" t="n">
-        <v>2.222222160458253</v>
+        <v>1.626806946053901</v>
       </c>
       <c r="J145" t="n">
         <v>2</v>
@@ -7259,11 +7259,11 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.15</v>
+        <v>1.1</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -7287,14 +7287,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>IT0005386369</t>
+          <t>IT0005253205</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>3.079999923706055</v>
+        <v>29.10000038146973</v>
       </c>
       <c r="I146" t="n">
-        <v>4.870129990766698</v>
+        <v>3.780068678969699</v>
       </c>
       <c r="J146" t="n">
         <v>2</v>
@@ -7306,11 +7306,11 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.7</v>
+        <v>0.47</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -7334,14 +7334,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>IT0001268561</t>
+          <t>IT0005107492</t>
         </is>
       </c>
       <c r="H147" t="n">
-        <v>12.25</v>
+        <v>55.09999847412109</v>
       </c>
       <c r="I147" t="n">
-        <v>5.714285714285714</v>
+        <v>0.8529945789757973</v>
       </c>
       <c r="J147" t="n">
         <v>2</v>
@@ -7353,11 +7353,11 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5105</v>
+        <v>1.2</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -7381,14 +7381,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>IT0001041000</t>
+          <t>IT0005274094</t>
         </is>
       </c>
       <c r="H148" t="n">
-        <v>9.220000267028809</v>
+        <v>78.80000305175781</v>
       </c>
       <c r="I148" t="n">
-        <v>5.536876195389864</v>
+        <v>1.522842580617427</v>
       </c>
       <c r="J148" t="n">
         <v>2</v>
@@ -7400,7 +7400,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>DOLLARI USA</t>
+          <t>EURO</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7428,14 +7428,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>LU2592315662</t>
+          <t>IT0005513202</t>
         </is>
       </c>
       <c r="H149" t="n">
-        <v>8</v>
+        <v>25.5</v>
       </c>
       <c r="I149" t="n">
-        <v>3.375</v>
+        <v>1.058823529411765</v>
       </c>
       <c r="J149" t="n">
         <v>2</v>
@@ -7447,11 +7447,11 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -7475,14 +7475,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>IT0003850929</t>
+          <t>IT0001018362</t>
         </is>
       </c>
       <c r="H150" t="n">
-        <v>5.744999885559082</v>
+        <v>10.30000019073486</v>
       </c>
       <c r="I150" t="n">
-        <v>6.092254255387845</v>
+        <v>3.689320320030873</v>
       </c>
       <c r="J150" t="n">
         <v>2</v>
@@ -7494,11 +7494,11 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -7522,14 +7522,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>IT0005203424</t>
+          <t>IT0005440893</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>39</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="I151" t="n">
-        <v>2.820512820512821</v>
+        <v>0.9933774583481174</v>
       </c>
       <c r="J151" t="n">
         <v>2</v>
@@ -7541,11 +7541,11 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.75</v>
+        <v>0.007</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -7554,45 +7554,45 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Straordinario</t>
+          <t>Ordinario</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>IT0005252736</t>
+          <t>IT0001073045</t>
         </is>
       </c>
       <c r="H152" t="n">
-        <v>18.85000038146973</v>
+        <v>0.1860000044107437</v>
       </c>
       <c r="I152" t="n">
-        <v>3.97877976032976</v>
+        <v>3.763440770970039</v>
       </c>
       <c r="J152" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="K152" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.43</v>
+        <v>0.16</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -7601,12 +7601,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7616,30 +7616,30 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>IT0003203947</t>
+          <t>IT0001033700</t>
         </is>
       </c>
       <c r="H153" t="n">
-        <v>11.69999980926514</v>
+        <v>7.21999979019165</v>
       </c>
       <c r="I153" t="n">
-        <v>3.675213735127469</v>
+        <v>2.216066546391865</v>
       </c>
       <c r="J153" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="K153" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.15</v>
+        <v>0.065</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -7648,12 +7648,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -7663,30 +7663,30 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>IT0005322612</t>
+          <t>IT0003372205</t>
         </is>
       </c>
       <c r="H154" t="n">
-        <v>4.260000228881836</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="I154" t="n">
-        <v>3.521126571379833</v>
+        <v>2.954545390507408</v>
       </c>
       <c r="J154" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="K154" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.197169</v>
+        <v>0.25</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -7695,12 +7695,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -7710,30 +7710,30 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>IT0005455875</t>
+          <t>IT0003365613</t>
         </is>
       </c>
       <c r="H155" t="n">
-        <v>12.11999988555908</v>
+        <v>7.440000057220459</v>
       </c>
       <c r="I155" t="n">
-        <v>1.626806946053901</v>
+        <v>3.360215027920289</v>
       </c>
       <c r="J155" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="K155" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>I.M.D. International Medical Devices S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>1.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -7742,12 +7742,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -7757,30 +7757,30 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>IT0005253205</t>
+          <t>IT0005549255</t>
         </is>
       </c>
       <c r="H156" t="n">
-        <v>29.10000038146973</v>
+        <v>1.389999985694885</v>
       </c>
       <c r="I156" t="n">
-        <v>3.780068678969699</v>
+        <v>5.035971274849027</v>
       </c>
       <c r="J156" t="n">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="K156" t="n">
-        <v>4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -7789,12 +7789,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7804,30 +7804,30 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>IT0005107492</t>
+          <t>IT0004998065</t>
         </is>
       </c>
       <c r="H157" t="n">
-        <v>55.09999847412109</v>
+        <v>6.659999847412109</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8529945789757973</v>
+        <v>7.507507679512727</v>
       </c>
       <c r="J157" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="K157" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1.2</v>
+        <v>0.65</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -7836,12 +7836,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -7851,30 +7851,30 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>IT0005274094</t>
+          <t>IT0004776628</t>
         </is>
       </c>
       <c r="H158" t="n">
-        <v>78.80000305175781</v>
+        <v>18.6299991607666</v>
       </c>
       <c r="I158" t="n">
-        <v>1.522842580617427</v>
+        <v>3.488996399789711</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="K158" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -7883,12 +7883,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7898,30 +7898,30 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>IT0005513202</t>
+          <t>IT0005218380</t>
         </is>
       </c>
       <c r="H159" t="n">
-        <v>25.5</v>
+        <v>12.38500022888184</v>
       </c>
       <c r="I159" t="n">
-        <v>1.058823529411765</v>
+        <v>4.360112959390339</v>
       </c>
       <c r="J159" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="K159" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0.38</v>
+        <v>0.1</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7945,30 +7945,30 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>IT0001018362</t>
+          <t>NL0015435975</t>
         </is>
       </c>
       <c r="H160" t="n">
-        <v>10.30000019073486</v>
+        <v>6.300000190734863</v>
       </c>
       <c r="I160" t="n">
-        <v>3.689320320030873</v>
+        <v>1.587301539245438</v>
       </c>
       <c r="J160" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="K160" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -7977,12 +7977,12 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -7992,30 +7992,30 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>IT0005440893</t>
+          <t>IT0005215329</t>
         </is>
       </c>
       <c r="H161" t="n">
-        <v>30.20000076293945</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I161" t="n">
-        <v>0.9933774583481174</v>
+        <v>1.731601774494826</v>
       </c>
       <c r="J161" t="n">
-        <v>2</v>
+        <v>-12</v>
       </c>
       <c r="K161" t="n">
-        <v>4</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>0.007</v>
+        <v>3.615</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -8024,12 +8024,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8039,30 +8039,30 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>IT0001073045</t>
+          <t>NL0011585146</t>
         </is>
       </c>
       <c r="H162" t="n">
-        <v>0.1860000044107437</v>
+        <v>293.3500061035156</v>
       </c>
       <c r="I162" t="n">
-        <v>3.763440770970039</v>
+        <v>1.232316320022288</v>
       </c>
       <c r="J162" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="K162" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>0.16</v>
+        <v>1.36</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -8071,12 +8071,12 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8086,30 +8086,30 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>IT0001033700</t>
+          <t>IT0005144784</t>
         </is>
       </c>
       <c r="H163" t="n">
-        <v>7.21999979019165</v>
+        <v>30.89999961853027</v>
       </c>
       <c r="I163" t="n">
-        <v>2.216066546391865</v>
+        <v>4.401294552717173</v>
       </c>
       <c r="J163" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="K163" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>0.065</v>
+        <v>5.8216</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -8118,45 +8118,45 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Ordinario</t>
+          <t>Straordinario</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>IT0003372205</t>
+          <t>NL0015000LU4</t>
         </is>
       </c>
       <c r="H164" t="n">
-        <v>2.200000047683716</v>
+        <v>13.96500015258789</v>
       </c>
       <c r="I164" t="n">
-        <v>2.954545390507408</v>
+        <v>41.68707437444019</v>
       </c>
       <c r="J164" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="K164" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>MAIRE S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>0.25</v>
+        <v>0.585</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -8165,12 +8165,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8180,30 +8180,30 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>IT0003365613</t>
+          <t>IT0004931058</t>
         </is>
       </c>
       <c r="H165" t="n">
-        <v>7.440000057220459</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="I165" t="n">
-        <v>3.360215027920289</v>
+        <v>3.726114694949043</v>
       </c>
       <c r="J165" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="K165" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>I.M.D. International Medical Devices S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -8212,12 +8212,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -8227,30 +8227,30 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>IT0005549255</t>
+          <t>IT0000062957</t>
         </is>
       </c>
       <c r="H166" t="n">
-        <v>1.389999985694885</v>
+        <v>19.84499931335449</v>
       </c>
       <c r="I166" t="n">
-        <v>5.035971274849027</v>
+        <v>3.174603284445809</v>
       </c>
       <c r="J166" t="n">
-        <v>-5</v>
+        <v>-12</v>
       </c>
       <c r="K166" t="n">
-        <v>-3</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -8274,14 +8274,14 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>IT0004998065</t>
+          <t>IT0004176001</t>
         </is>
       </c>
       <c r="H167" t="n">
-        <v>6.659999847412109</v>
+        <v>127.9499969482422</v>
       </c>
       <c r="I167" t="n">
-        <v>7.507507679512727</v>
+        <v>0.7033997823103226</v>
       </c>
       <c r="J167" t="n">
         <v>-12</v>
@@ -8293,11 +8293,11 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>0.65</v>
+        <v>1.7208</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -8321,14 +8321,14 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>IT0004776628</t>
+          <t>IT0005239360</t>
         </is>
       </c>
       <c r="H168" t="n">
-        <v>18.6299991607666</v>
+        <v>65.62000274658203</v>
       </c>
       <c r="I168" t="n">
-        <v>3.488996399789711</v>
+        <v>2.622371118522441</v>
       </c>
       <c r="J168" t="n">
         <v>-12</v>
@@ -8340,11 +8340,11 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>I.CO.P. S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>0.54</v>
+        <v>0.14</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8368,30 +8368,30 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>IT0005218380</t>
+          <t>IT0001214433</t>
         </is>
       </c>
       <c r="H169" t="n">
-        <v>12.38500022888184</v>
+        <v>26.79999923706055</v>
       </c>
       <c r="I169" t="n">
-        <v>4.360112959390339</v>
+        <v>0.5223880745727789</v>
       </c>
       <c r="J169" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K169" t="n">
-        <v>-10</v>
+        <v>-17</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -8400,12 +8400,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -8415,489 +8415,19 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>NL0015435975</t>
+          <t>IT0005418204</t>
         </is>
       </c>
       <c r="H170" t="n">
-        <v>6.300000190734863</v>
+        <v>1.529999971389771</v>
       </c>
       <c r="I170" t="n">
-        <v>1.587301539245438</v>
+        <v>3.92156870078234</v>
       </c>
       <c r="J170" t="n">
-        <v>-12</v>
+        <v>-19</v>
       </c>
       <c r="K170" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B171" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>IT0005215329</t>
-        </is>
-      </c>
-      <c r="H171" t="n">
-        <v>9.239999771118164</v>
-      </c>
-      <c r="I171" t="n">
-        <v>1.731601774494826</v>
-      </c>
-      <c r="J171" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K171" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Ferrari N.V.</t>
-        </is>
-      </c>
-      <c r="B172" t="n">
-        <v>3.615</v>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>NL0011585146</t>
-        </is>
-      </c>
-      <c r="H172" t="n">
-        <v>293.3500061035156</v>
-      </c>
-      <c r="I172" t="n">
-        <v>1.232316320022288</v>
-      </c>
-      <c r="J172" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K172" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B173" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>IT0005144784</t>
-        </is>
-      </c>
-      <c r="H173" t="n">
-        <v>30.89999961853027</v>
-      </c>
-      <c r="I173" t="n">
-        <v>4.401294552717173</v>
-      </c>
-      <c r="J173" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K173" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Iveco Group N.V.</t>
-        </is>
-      </c>
-      <c r="B174" t="n">
-        <v>5.8216</v>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>Straordinario</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>NL0015000LU4</t>
-        </is>
-      </c>
-      <c r="H174" t="n">
-        <v>13.96500015258789</v>
-      </c>
-      <c r="I174" t="n">
-        <v>41.68707437444019</v>
-      </c>
-      <c r="J174" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K174" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>MAIRE S.p.A.</t>
-        </is>
-      </c>
-      <c r="B175" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>IT0004931058</t>
-        </is>
-      </c>
-      <c r="H175" t="n">
-        <v>15.69999980926514</v>
-      </c>
-      <c r="I175" t="n">
-        <v>3.726114694949043</v>
-      </c>
-      <c r="J175" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K175" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
-        </is>
-      </c>
-      <c r="B176" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>IT0000062957</t>
-        </is>
-      </c>
-      <c r="H176" t="n">
-        <v>19.84499931335449</v>
-      </c>
-      <c r="I176" t="n">
-        <v>3.174603284445809</v>
-      </c>
-      <c r="J176" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K176" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Prysmian S.p.A.</t>
-        </is>
-      </c>
-      <c r="B177" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>IT0004176001</t>
-        </is>
-      </c>
-      <c r="H177" t="n">
-        <v>127.9499969482422</v>
-      </c>
-      <c r="I177" t="n">
-        <v>0.7033997823103226</v>
-      </c>
-      <c r="J177" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K177" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Unicredit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B178" t="n">
-        <v>1.7208</v>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>IT0005239360</t>
-        </is>
-      </c>
-      <c r="H178" t="n">
-        <v>65.62000274658203</v>
-      </c>
-      <c r="I178" t="n">
-        <v>2.622371118522441</v>
-      </c>
-      <c r="J178" t="n">
-        <v>-12</v>
-      </c>
-      <c r="K178" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>I.CO.P. S.p.A. Società Benefit</t>
-        </is>
-      </c>
-      <c r="B179" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>IT0001214433</t>
-        </is>
-      </c>
-      <c r="H179" t="n">
-        <v>26.79999923706055</v>
-      </c>
-      <c r="I179" t="n">
-        <v>0.5223880745727789</v>
-      </c>
-      <c r="J179" t="n">
-        <v>-19</v>
-      </c>
-      <c r="K179" t="n">
-        <v>-17</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Reti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B180" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>2026-04-13</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>Ordinario</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>IT0005418204</t>
-        </is>
-      </c>
-      <c r="H180" t="n">
-        <v>1.529999971389771</v>
-      </c>
-      <c r="I180" t="n">
-        <v>3.92156870078234</v>
-      </c>
-      <c r="J180" t="n">
-        <v>-19</v>
-      </c>
-      <c r="K180" t="n">
         <v>-17</v>
       </c>
     </row>
@@ -9836,7 +9366,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9870,7 +9400,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9880,14 +9410,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -9897,14 +9427,14 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -9921,7 +9451,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -9931,7 +9461,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -9948,14 +9478,14 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -9965,14 +9495,14 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -9982,14 +9512,14 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -10006,7 +9536,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -10023,7 +9553,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -10033,14 +9563,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -10050,14 +9580,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10074,7 +9604,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -10084,14 +9614,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -10108,7 +9638,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10125,7 +9655,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10142,7 +9672,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10152,14 +9682,14 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -10169,14 +9699,14 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10186,14 +9716,14 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10203,14 +9733,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10227,7 +9757,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10237,14 +9767,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10254,14 +9784,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10288,14 +9818,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10305,7 +9835,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -10322,14 +9852,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10339,14 +9869,14 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10356,14 +9886,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10380,7 +9910,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10397,7 +9927,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10407,14 +9937,14 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10424,14 +9954,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10458,14 +9988,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10482,7 +10012,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10509,14 +10039,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10526,14 +10056,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10771,7 +10301,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10781,14 +10311,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10798,14 +10328,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10815,14 +10345,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10832,14 +10362,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10856,7 +10386,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10873,7 +10403,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10883,14 +10413,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10907,7 +10437,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10917,14 +10447,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10975,7 +10505,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10992,7 +10522,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11009,7 +10539,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11019,14 +10549,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -11043,7 +10573,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11060,7 +10590,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11077,7 +10607,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11094,7 +10624,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11111,7 +10641,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11121,14 +10651,14 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11145,7 +10675,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11155,14 +10685,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11172,14 +10702,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11189,14 +10719,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11206,14 +10736,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11230,7 +10760,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11240,14 +10770,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11264,7 +10794,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11274,14 +10804,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11298,7 +10828,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11308,14 +10838,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11332,7 +10862,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11342,14 +10872,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11359,14 +10889,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11376,14 +10906,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11400,7 +10930,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11410,14 +10940,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11427,14 +10957,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11444,14 +10974,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11461,14 +10991,14 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11478,14 +11008,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11495,14 +11025,14 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11519,7 +11049,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11529,14 +11059,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11553,7 +11083,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11570,7 +11100,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11580,14 +11110,14 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11597,14 +11127,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11621,7 +11151,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11631,14 +11161,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11648,14 +11178,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11672,7 +11202,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11682,14 +11212,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11706,7 +11236,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11716,14 +11246,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11740,7 +11270,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11750,14 +11280,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11767,14 +11297,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11791,7 +11321,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11801,14 +11331,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11825,7 +11355,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11842,7 +11372,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11852,14 +11382,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11869,14 +11399,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11893,7 +11423,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11903,14 +11433,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11927,7 +11457,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11944,7 +11474,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11954,14 +11484,14 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11971,14 +11501,14 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11988,7 +11518,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -12012,7 +11542,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12029,7 +11559,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12046,7 +11576,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12056,14 +11586,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12080,7 +11610,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12090,14 +11620,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12114,7 +11644,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12124,14 +11654,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12148,7 +11678,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12165,7 +11695,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12175,14 +11705,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12192,14 +11722,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12216,7 +11746,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12226,14 +11756,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12250,7 +11780,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12267,7 +11797,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12284,7 +11814,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12301,7 +11831,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12318,7 +11848,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12335,7 +11865,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12345,14 +11875,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12362,7 +11892,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12386,7 +11916,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12396,14 +11926,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12420,7 +11950,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12430,14 +11960,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12454,7 +11984,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12464,14 +11994,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12481,14 +12011,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12505,7 +12035,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12515,14 +12045,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12539,7 +12069,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12549,14 +12079,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12573,7 +12103,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12590,7 +12120,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12607,7 +12137,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12624,7 +12154,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12641,7 +12171,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12658,7 +12188,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12668,7 +12198,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -12685,14 +12215,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12702,14 +12232,14 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12719,14 +12249,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -12743,7 +12273,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12760,7 +12290,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12777,7 +12307,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12794,7 +12324,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12804,14 +12334,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12828,7 +12358,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12845,7 +12375,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12855,14 +12385,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12879,7 +12409,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12889,14 +12419,14 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12913,7 +12443,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12930,7 +12460,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12940,14 +12470,14 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12964,7 +12494,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12981,7 +12511,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12998,7 +12528,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13008,14 +12538,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13032,7 +12562,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13042,14 +12572,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13059,14 +12589,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -13083,7 +12613,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13093,14 +12623,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13110,14 +12640,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13134,7 +12664,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13144,14 +12674,14 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13168,7 +12698,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13178,14 +12708,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13195,14 +12725,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13212,14 +12742,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13229,14 +12759,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13253,7 +12783,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13263,14 +12793,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13287,7 +12817,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13304,7 +12834,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13321,7 +12851,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13331,14 +12861,14 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13348,14 +12878,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13365,14 +12895,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -13389,7 +12919,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13406,7 +12936,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13416,14 +12946,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13433,14 +12963,14 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13450,14 +12980,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -13467,14 +12997,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13491,7 +13021,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13501,14 +13031,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13518,14 +13048,14 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13535,14 +13065,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13552,7 +13082,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -13576,7 +13106,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13586,14 +13116,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13603,14 +13133,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13620,7 +13150,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -13644,7 +13174,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13654,14 +13184,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13671,14 +13201,14 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>DIADEMA CAPITAL</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13695,7 +13225,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>DIADEMA CAPITAL</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13705,14 +13235,14 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13722,14 +13252,14 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13763,7 +13293,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13773,14 +13303,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13790,14 +13320,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13807,14 +13337,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13824,14 +13354,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13841,14 +13371,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13865,7 +13395,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13882,7 +13412,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13892,7 +13422,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -13916,7 +13446,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13926,14 +13456,14 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -13943,14 +13473,14 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13960,14 +13490,14 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13977,14 +13507,14 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -13994,7 +13524,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -14052,7 +13582,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14069,7 +13599,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14086,7 +13616,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>E-NOVIA S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14096,14 +13626,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14113,7 +13643,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -14137,7 +13667,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14147,14 +13677,14 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>E-NOVIA S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14164,14 +13694,14 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14256,7 +13786,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14273,7 +13803,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14283,14 +13813,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14300,14 +13830,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14324,7 +13854,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14334,14 +13864,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14358,7 +13888,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14375,7 +13905,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14392,7 +13922,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14409,7 +13939,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14419,14 +13949,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14443,7 +13973,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14453,14 +13983,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14470,14 +14000,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14487,14 +14017,14 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14504,14 +14034,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14528,7 +14058,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14538,14 +14068,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14555,14 +14085,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14572,14 +14102,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14589,14 +14119,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>H-FARM S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14606,14 +14136,14 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14647,7 +14177,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14664,7 +14194,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>H-FARM S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14674,14 +14204,14 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -14691,14 +14221,14 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -14715,7 +14245,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14725,14 +14255,14 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14742,14 +14272,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14759,14 +14289,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14776,14 +14306,14 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14793,14 +14323,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14810,7 +14340,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
